--- a/app/Services/data.xlsx
+++ b/app/Services/data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="inventory" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="stock_entries" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="uniform_categories" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,11 +463,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Uniform - Shirt (Long) - Boy - Size M</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -490,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,15 +522,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>uniform_category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>given_to</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>admin_name</t>
         </is>
@@ -557,17 +563,18 @@
       <c r="E2" t="n">
         <v>-1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Nyan Zin Htun</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>ITPEC B12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Nyan Zin Htun</t>
         </is>
@@ -597,7 +604,8 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>NiT</t>
         </is>
@@ -625,17 +633,18 @@
       <c r="E4" t="n">
         <v>98</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Sir Phay Chit</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Sir Phay Chit</t>
         </is>
@@ -663,17 +672,18 @@
       <c r="E5" t="n">
         <v>97</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Tr Zar Ni</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Tr Zar Ni</t>
         </is>
@@ -701,17 +711,18 @@
       <c r="E6" t="n">
         <v>96</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Tr Han Su</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Tr Han Su</t>
         </is>
@@ -739,17 +750,18 @@
       <c r="E7" t="n">
         <v>95</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Tr Thwet Thuzar</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Tr Thwet Thuzar</t>
         </is>
@@ -777,17 +789,18 @@
       <c r="E8" t="n">
         <v>94</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Ma Htet</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Ma Htet</t>
         </is>
@@ -815,17 +828,18 @@
       <c r="E9" t="n">
         <v>-1</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Aung Khant Bwar (Institute)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Aung Khant Bwar (Institute)</t>
         </is>
@@ -834,12 +848,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-22T07:04:33.455084+00:00</t>
+          <t>2026-02-22T01:39:00+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Water Bottle</t>
+          <t>Uniform - Shirt (Long) - Boy - Size M</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -848,14 +862,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Uniform - Shirt (Long) - Boy - Size M</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NiT</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>NiT</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>NiT</t>
         </is>
@@ -864,12 +891,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-22T07:04:33.455084+00:00</t>
+          <t>2026-02-22T14:25:51.412710+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Note Book</t>
+          <t>Water Bottle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -878,14 +905,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>NiT</t>
         </is>
@@ -894,12 +922,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-22T07:04:33.455084+00:00</t>
+          <t>2026-02-22T14:25:51.412710+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Umbrella</t>
+          <t>Note Book</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -908,14 +936,15 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>NiT</t>
         </is>
@@ -924,28 +953,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-22T07:22:35.099832+00:00</t>
+          <t>2026-02-22T14:25:51.412710+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Umbrella</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>NiT</t>
         </is>
@@ -973,17 +1003,18 @@
       <c r="E14" t="n">
         <v>93</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Thiha Naing</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Thiha Naing</t>
         </is>
@@ -1011,17 +1042,18 @@
       <c r="E15" t="n">
         <v>92</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Hsu Pachi Moe</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Hsu Pachi Moe</t>
         </is>
@@ -1049,17 +1081,18 @@
       <c r="E16" t="n">
         <v>91</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Thigi Soe</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Thigi Soe</t>
         </is>
@@ -1087,17 +1120,18 @@
       <c r="E17" t="n">
         <v>90</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Phyu Sin La Min</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Phyu Sin La Min</t>
         </is>
@@ -1125,17 +1159,18 @@
       <c r="E18" t="n">
         <v>89</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Su Sandar Kyaw</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Su Sandar Kyaw</t>
         </is>
@@ -1163,17 +1198,18 @@
       <c r="E19" t="n">
         <v>88</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>U Nyein Chan</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>U Nyein Chan</t>
         </is>
@@ -1201,17 +1237,18 @@
       <c r="E20" t="n">
         <v>87</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Wint Htet Htet</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Wint Htet Htet</t>
         </is>
@@ -1239,17 +1276,18 @@
       <c r="E21" t="n">
         <v>86</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Thae Htet Myat</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Thae Htet Myat</t>
         </is>
@@ -1277,17 +1315,18 @@
       <c r="E22" t="n">
         <v>85</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Aung Thiha</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Designer</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Aung Thiha</t>
         </is>
@@ -1315,17 +1354,18 @@
       <c r="E23" t="n">
         <v>84</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Aung Myat Thu</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Aung Myat Thu</t>
         </is>
@@ -1353,17 +1393,18 @@
       <c r="E24" t="n">
         <v>77</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Parent (Ncc + IP)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Orientation</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Parent (Ncc + IP)</t>
         </is>
@@ -1391,13 +1432,14 @@
       <c r="E25" t="n">
         <v>76</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Institute Reception</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Institute Reception</t>
         </is>
@@ -1425,17 +1467,18 @@
       <c r="E26" t="n">
         <v>75</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Thin Htet</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Thin Htet</t>
         </is>
@@ -1463,17 +1506,18 @@
       <c r="E27" t="n">
         <v>10</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Java Batch 4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
@@ -1501,20 +1545,73 @@
       <c r="E28" t="n">
         <v>74</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Java Batch 4</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>uniform_category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>in_quantity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>out_quantity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Uniform - Shirt (Long) - Boy - Size M</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/app/Services/data.xlsx
+++ b/app/Services/data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,20 +463,10 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uniform - Shirt (Long) - Boy - Size M</t>
+          <t>Water Bottle</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Water Bottle</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
         <v>34</v>
       </c>
     </row>
@@ -491,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,12 +838,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-22T01:39:00+00:00</t>
+          <t>2026-02-22T14:30:32.892275+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uniform - Shirt (Long) - Boy - Size M</t>
+          <t>Water Bottle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -862,26 +852,14 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Uniform - Shirt (Long) - Boy - Size M</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NiT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>NiT</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>NiT</t>
@@ -891,12 +869,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-22T14:25:51.412710+00:00</t>
+          <t>2026-02-22T14:30:32.892275+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Water Bottle</t>
+          <t>Note Book</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,10 +883,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -922,12 +900,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-22T14:25:51.412710+00:00</t>
+          <t>2026-02-22T14:30:32.892275+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Note Book</t>
+          <t>Umbrella</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -936,10 +914,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -953,31 +931,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-22T14:25:51.412710+00:00</t>
+          <t>2026-04-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Umbrella</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thiha Naing</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NiT</t>
+          <t>Thiha Naing</t>
         </is>
       </c>
     </row>
@@ -1001,12 +987,12 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thiha Naing</t>
+          <t>Hsu Pachi Moe</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1016,7 +1002,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Thiha Naing</t>
+          <t>Hsu Pachi Moe</t>
         </is>
       </c>
     </row>
@@ -1040,22 +1026,22 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hsu Pachi Moe</t>
+          <t>Thigi Soe</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hsu Pachi Moe</t>
+          <t>Thigi Soe</t>
         </is>
       </c>
     </row>
@@ -1079,22 +1065,22 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thigi Soe</t>
+          <t>Phyu Sin La Min</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Thigi Soe</t>
+          <t>Phyu Sin La Min</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1104,12 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phyu Sin La Min</t>
+          <t>Su Sandar Kyaw</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1133,7 +1119,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Phyu Sin La Min</t>
+          <t>Su Sandar Kyaw</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1143,12 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Su Sandar Kyaw</t>
+          <t>U Nyein Chan</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1172,7 +1158,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Su Sandar Kyaw</t>
+          <t>U Nyein Chan</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1182,12 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>U Nyein Chan</t>
+          <t>Wint Htet Htet</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1211,7 +1197,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>U Nyein Chan</t>
+          <t>Wint Htet Htet</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1221,12 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wint Htet Htet</t>
+          <t>Thae Htet Myat</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1250,14 +1236,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Wint Htet Htet</t>
+          <t>Thae Htet Myat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-30T17:30:00+00:00</t>
+          <t>2026-05-31T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1274,22 +1260,22 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thae Htet Myat</t>
+          <t>Aung Thiha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Thae Htet Myat</t>
+          <t>Aung Thiha</t>
         </is>
       </c>
     </row>
@@ -1313,29 +1299,29 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aung Thiha</t>
+          <t>Aung Myat Thu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aung Thiha</t>
+          <t>Aung Myat Thu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-31T17:30:00+00:00</t>
+          <t>2026-06-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1349,25 +1335,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Aung Myat Thu</t>
+          <t>Parent (Ncc + IP)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Orientation</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aung Myat Thu</t>
+          <t>Parent (Ncc + IP)</t>
         </is>
       </c>
     </row>
@@ -1388,25 +1374,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parent (Ncc + IP)</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
+          <t>Institute Reception</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Parent (Ncc + IP)</t>
+          <t>Institute Reception</t>
         </is>
       </c>
     </row>
@@ -1430,30 +1412,34 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Institute Reception</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Thin Htet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Institute Reception</t>
+          <t>Thin Htet</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-30T17:30:00+00:00</t>
+          <t>2026-09-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Note Book</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1465,22 +1451,22 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thin Htet</t>
+          <t>Zin MinThet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Java Batch 4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Thin Htet</t>
+          <t>Zin MinThet</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1478,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Note Book</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1504,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -1518,45 +1504,6 @@
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>Zin MinThet</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-30T17:30:00+00:00</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>74</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Zin MinThet</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Java Batch 4</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
@@ -1573,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,22 +1545,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Uniform - Shirt (Long) - Boy - Size M</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/Services/data.xlsx
+++ b/app/Services/data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,10 +463,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Uniform - Shirt (Long) - Boy - Size 2XL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Water Bottle</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>34</v>
       </c>
     </row>
@@ -481,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,78 +951,74 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-30T17:30:00+00:00</t>
+          <t>2026-02-23T09:16:00+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Uniform - Shirt (Long) - Boy - Size 2XL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Uniform - Shirt (Long) - Boy - Size 2XL</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thiha Naing</t>
+          <t>Eaint Htoo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Thiha Naing</t>
+          <t>NiT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-30T17:30:00+00:00</t>
+          <t>2026-02-23T09:17:59.459744+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hsu Pachi Moe</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hsu Pachi Moe</t>
+          <t>NiT</t>
         </is>
       </c>
     </row>
@@ -1026,22 +1042,22 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thigi Soe</t>
+          <t>Thiha Naing</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Thigi Soe</t>
+          <t>Thiha Naing</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1081,12 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phyu Sin La Min</t>
+          <t>Hsu Pachi Moe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1080,7 +1096,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Phyu Sin La Min</t>
+          <t>Hsu Pachi Moe</t>
         </is>
       </c>
     </row>
@@ -1104,22 +1120,22 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Su Sandar Kyaw</t>
+          <t>Thigi Soe</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Su Sandar Kyaw</t>
+          <t>Thigi Soe</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1159,12 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>U Nyein Chan</t>
+          <t>Phyu Sin La Min</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1158,7 +1174,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>U Nyein Chan</t>
+          <t>Phyu Sin La Min</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Wint Htet Htet</t>
+          <t>Su Sandar Kyaw</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1197,7 +1213,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Wint Htet Htet</t>
+          <t>Su Sandar Kyaw</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1237,12 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thae Htet Myat</t>
+          <t>U Nyein Chan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1236,14 +1252,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Thae Htet Myat</t>
+          <t>U Nyein Chan</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-31T17:30:00+00:00</t>
+          <t>2026-04-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1260,29 +1276,29 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Aung Thiha</t>
+          <t>Wint Htet Htet</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aung Thiha</t>
+          <t>Wint Htet Htet</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-31T17:30:00+00:00</t>
+          <t>2026-04-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1299,12 +1315,12 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aung Myat Thu</t>
+          <t>Thae Htet Myat</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1314,14 +1330,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aung Myat Thu</t>
+          <t>Thae Htet Myat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-30T17:30:00+00:00</t>
+          <t>2026-05-31T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1335,32 +1351,32 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parent (Ncc + IP)</t>
+          <t>Aung Thiha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Orientation</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Parent (Ncc + IP)</t>
+          <t>Aung Thiha</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-30T17:30:00+00:00</t>
+          <t>2026-05-31T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1377,18 +1393,22 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Institute Reception</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Aung Myat Thu</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Institute Reception</t>
+          <t>Aung Myat Thu</t>
         </is>
       </c>
     </row>
@@ -1409,37 +1429,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thin Htet</t>
+          <t>Parent (Ncc + IP)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Orientation</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Thin Htet</t>
+          <t>Parent (Ncc + IP)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30T17:30:00+00:00</t>
+          <t>2026-06-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Note Book</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1451,29 +1471,25 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zin MinThet</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Java Batch 4</t>
-        </is>
-      </c>
+          <t>Institute Reception</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Zin MinThet</t>
+          <t>Institute Reception</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30T17:30:00+00:00</t>
+          <t>2026-06-30T17:30:00+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1490,20 +1506,98 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Thin Htet</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Thin Htet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-30T17:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Note Book</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Zin MinThet</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Java Batch 4</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Zin MinThet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-30T17:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>74</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Zin MinThet</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Java Batch 4</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Zin MinThet</t>
         </is>
@@ -1520,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1545,6 +1639,22 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Uniform - Shirt (Long) - Boy - Size 2XL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
